--- a/Filament_Inventory_v4.xlsx
+++ b/Filament_Inventory_v4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Documents/GitHub/Unified-Filament-Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_EB550AEFE570474796F8012723DEBA19872CFD0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A814B86E-32A2-49B4-93D1-E610F392667D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_EB550AEFE570474796F8012723DEBA19872CFD0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF70AA90-FF23-4B52-8026-600866D3B899}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="450" windowWidth="26010" windowHeight="14145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,6 +844,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1566,11 +1570,11 @@
         <v>1000</v>
       </c>
       <c r="V3" s="5">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" ref="W3:W34" si="0">IF(V3="","",IF(U3="","",V3/U3))</f>
-        <v>0.10199999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>55</v>
@@ -1629,12 +1633,14 @@
         <v>54</v>
       </c>
       <c r="U4" s="5">
-        <v>970</v>
-      </c>
-      <c r="V4" s="5"/>
-      <c r="W4" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="V4" s="5">
+        <v>954</v>
+      </c>
+      <c r="W4" s="10">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.95399999999999996</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="9">
